--- a/out/MLP-Mamba1_repeat_5_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000006.xlsx
@@ -2527,14 +2527,14 @@
       </c>
       <c r="IZ2" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3322,14 +3322,14 @@
       </c>
       <c r="IZ3" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4919,7 +4919,7 @@
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.633306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5714,7 +5714,7 @@
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7304,7 +7304,7 @@
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8092,14 +8092,14 @@
       </c>
       <c r="IZ9" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8887,14 +8887,14 @@
       </c>
       <c r="IZ10" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10477,14 +10477,14 @@
       </c>
       <c r="IZ12" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12074,7 +12074,7 @@
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17639,7 +17639,7 @@
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.233306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21614,7 +21614,7 @@
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7138070993914605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7138070993914605</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27967,14 +27967,14 @@
       </c>
       <c r="IZ34" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29564,7 +29564,7 @@
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32737,14 +32737,14 @@
       </c>
       <c r="IZ40" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000356359406394884</v>
+        <v>-0.0003128222096160753</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4586623150920038</v>
+        <v>0.4026263409910837</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9181926399135468</v>
+        <v>0.806015066578293</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1059239810575001</v>
+        <v>-0.09298306858678258</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.633306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.3093304501946852</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.233306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3519922083080998</v>
+        <v>0.3090611464411744</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.19744626729591</v>
+        <v>0.8273593729251539</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.749269463479246</v>
+        <v>1.965427358179969</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2291178508372719</v>
+        <v>0.158305831513631</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.233306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.008311258729316</v>
+        <v>1.453472403560454</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4013216448407176</v>
+        <v>0.2772878948554011</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.633306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.581949320728867</v>
+        <v>1.849819837926228</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.219778575310485</v>
+        <v>0.1518529418944903</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.619838476051484</v>
+        <v>1.875998821448659</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09077175230178069</v>
+        <v>0.06271747648045552</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.5813730088882</v>
+        <v>1.849421643296335</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1130938138610675</v>
+        <v>0.07814059364344086</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.71680411994076</v>
+        <v>1.94299588095038</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06809649394743847</v>
+        <v>0.04705014038626072</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.739827730757266</v>
+        <v>1.958903724088574</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05177253967961519</v>
+        <v>0.03577165311867397</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.775246036014459</v>
+        <v>1.983375603149405</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02289912903417543</v>
+        <v>0.01582110087575931</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.633306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.769226091984594</v>
+        <v>1.979216191904165</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0181693706185043</v>
+        <v>0.01255309261819042</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.633306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.782659980561601</v>
+        <v>1.988497582471814</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009007833388688085</v>
+        <v>0.006223685855629567</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.782494103097988</v>
+        <v>1.988381415888184</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005237379743624433</v>
+        <v>0.003616954928308779</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.783953766027672</v>
+        <v>1.989388350043265</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002616189871812217</v>
+        <v>0.001804522863781575</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.783945502469337</v>
+        <v>1.989381097065147</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001288591673071766</v>
+        <v>0.0008890155785007095</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.633306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.783907721901414</v>
+        <v>1.989353431364695</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007459718750281157</v>
+        <v>0.000515673833352827</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.784110857057088</v>
+        <v>1.989492417003745</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002472126228788256</v>
+        <v>0.0001690936688898088</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.783855355193342</v>
+        <v>1.989314504212841</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001207643042471784</v>
+        <v>8.258585474357068e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.783851760640701</v>
+        <v>1.989310473369611</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.349349164303817e-05</v>
+        <v>4.147772647206162e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.783858111604302</v>
+        <v>1.989313240302476</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.870180446963262e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.233306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.783850862857269</v>
+        <v>1.989306688416747</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>9.546003728147707e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.783853932520712</v>
+        <v>1.989307066984992</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.783846262799617</v>
+        <v>1.989300400021122</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.783842777579309</v>
+        <v>1.989296537946026</v>
       </c>
     </row>
     <row r="71">
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.783838230267124</v>
+        <v>1.989291990633841</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.783838320211774</v>
+        <v>1.989292080578491</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.783837462278189</v>
+        <v>1.989291222644906</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.783837690599224</v>
+        <v>1.989291450965941</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.783836894935012</v>
+        <v>1.989290655301729</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.783836957204385</v>
+        <v>1.989290717571102</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.783836984879662</v>
+        <v>1.989290745246379</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.783837137093685</v>
+        <v>1.989290897460402</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.783836791152724</v>
+        <v>1.98929055151944</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.783836867259735</v>
+        <v>1.989290627626452</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.783837033311397</v>
+        <v>1.989290793678113</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.783837393089997</v>
+        <v>1.989291153456713</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.783837413846455</v>
+        <v>1.989291174213171</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.783837517628743</v>
+        <v>1.989291277995459</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.783837745949778</v>
+        <v>1.989291506316494</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.783837621411032</v>
+        <v>1.989291381777748</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.783837649086309</v>
+        <v>1.989291409453025</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.233306561630227</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.783837704436862</v>
+        <v>1.989291464803579</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.783837967351993</v>
+        <v>1.989291727718709</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.783837884326162</v>
+        <v>1.989291644692879</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.633306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.783837676761585</v>
+        <v>1.989291437128302</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.233306561630227</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.783837690599224</v>
+        <v>1.989291450965941</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.783837828975609</v>
+        <v>1.989291589342325</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.78383754530402</v>
+        <v>1.989291305670736</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.783837372333539</v>
+        <v>1.989291132700256</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.633306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.783837268551251</v>
+        <v>1.989291028917967</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.783837413846455</v>
+        <v>1.989291174213171</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.783837656005128</v>
+        <v>1.989291416371844</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.783837483034647</v>
+        <v>1.989291243401363</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.78383718552542</v>
+        <v>1.989290945892137</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.783837171687781</v>
+        <v>1.989290932054498</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.783836804990362</v>
+        <v>1.989290565357078</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.783836804990362</v>
+        <v>1.989290565357078</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.783836742720989</v>
+        <v>1.989290503087705</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.7838366389387</v>
+        <v>1.989290399305417</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.78383646596822</v>
+        <v>1.989290226334936</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.783836514399954</v>
+        <v>1.989290274766671</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.783836154621354</v>
+        <v>1.989289914988071</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.783836113108439</v>
+        <v>1.989289873475155</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.783836168458993</v>
+        <v>1.989289928825709</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.783836223809547</v>
+        <v>1.989289984176263</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.783836265322462</v>
+        <v>1.989290025689179</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.783835995488512</v>
+        <v>1.989289755855228</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.783836050839065</v>
+        <v>1.989289811205782</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.78383619613427</v>
+        <v>1.989289956500986</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.783836161540174</v>
+        <v>1.98928992190689</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.783836147702535</v>
+        <v>1.989289908069252</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.783836237647185</v>
+        <v>1.989289998013902</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.783836555912869</v>
+        <v>1.989290316279586</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.9612393007297437</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.78383637602357</v>
+        <v>1.989290136390286</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.783836417536485</v>
+        <v>1.989290177903202</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.783836230728366</v>
+        <v>1.989289991095082</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.783836299916558</v>
+        <v>1.989290060283274</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.313807099391461</v>
+        <v>-1.561239300729744</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.7838360992708</v>
+        <v>1.989289859637517</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.313807099391461</v>
+        <v>1.254026995542006</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.783836140783716</v>
+        <v>1.989289901150432</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.233306561630227</v>
+        <v>1.854026995542006</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.783836168458993</v>
+        <v>1.989289928825709</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000006.xlsx
@@ -2534,7 +2534,7 @@
         <v>0</v>
       </c>
       <c r="JB2" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3329,7 +3329,7 @@
         <v>0</v>
       </c>
       <c r="JB3" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4124,7 +4124,7 @@
         <v>0</v>
       </c>
       <c r="JB4" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA5" t="n">
         <v>1</v>
       </c>
       <c r="JB5" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5707,14 +5707,14 @@
       </c>
       <c r="IZ6" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA6" t="n">
         <v>0</v>
       </c>
       <c r="JB6" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6509,7 +6509,7 @@
         <v>1</v>
       </c>
       <c r="JB7" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA8" t="n">
         <v>0</v>
       </c>
       <c r="JB8" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8099,7 +8099,7 @@
         <v>0</v>
       </c>
       <c r="JB9" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8894,7 +8894,7 @@
         <v>0</v>
       </c>
       <c r="JB10" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="JB11" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="JB12" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="JB13" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12067,14 +12067,14 @@
       </c>
       <c r="IZ14" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA14" t="n">
         <v>1</v>
       </c>
       <c r="JB14" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA15" t="n">
         <v>0</v>
       </c>
       <c r="JB15" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13664,7 +13664,7 @@
         <v>0</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14459,7 +14459,7 @@
         <v>0</v>
       </c>
       <c r="JB17" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15254,7 +15254,7 @@
         <v>0</v>
       </c>
       <c r="JB18" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16049,7 +16049,7 @@
         <v>0</v>
       </c>
       <c r="JB19" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16844,7 +16844,7 @@
         <v>1</v>
       </c>
       <c r="JB20" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17632,14 +17632,14 @@
       </c>
       <c r="IZ21" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA21" t="n">
         <v>0</v>
       </c>
       <c r="JB21" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18434,7 +18434,7 @@
         <v>0</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19229,7 +19229,7 @@
         <v>0</v>
       </c>
       <c r="JB23" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20024,7 +20024,7 @@
         <v>0</v>
       </c>
       <c r="JB24" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20819,7 +20819,7 @@
         <v>1</v>
       </c>
       <c r="JB25" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21607,14 +21607,14 @@
       </c>
       <c r="IZ26" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA26" t="n">
         <v>0</v>
       </c>
       <c r="JB26" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>1</v>
       </c>
       <c r="JB27" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23197,14 +23197,14 @@
       </c>
       <c r="IZ28" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA28" t="n">
         <v>0</v>
       </c>
       <c r="JB28" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23999,7 +23999,7 @@
         <v>0</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24794,7 +24794,7 @@
         <v>0</v>
       </c>
       <c r="JB30" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25589,7 +25589,7 @@
         <v>0</v>
       </c>
       <c r="JB31" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26384,7 +26384,7 @@
         <v>0</v>
       </c>
       <c r="JB32" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27179,7 +27179,7 @@
         <v>0</v>
       </c>
       <c r="JB33" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27974,7 +27974,7 @@
         <v>0</v>
       </c>
       <c r="JB34" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28769,7 +28769,7 @@
         <v>1</v>
       </c>
       <c r="JB35" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA36" t="n">
         <v>0</v>
       </c>
       <c r="JB36" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30359,7 +30359,7 @@
         <v>0</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31154,7 +31154,7 @@
         <v>0</v>
       </c>
       <c r="JB38" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31949,7 +31949,7 @@
         <v>0</v>
       </c>
       <c r="JB39" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32744,7 +32744,7 @@
         <v>0</v>
       </c>
       <c r="JB40" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33539,7 +33539,7 @@
         <v>0</v>
       </c>
       <c r="JB41" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34334,7 +34334,7 @@
         <v>1</v>
       </c>
       <c r="JB42" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35129,7 +35129,7 @@
         <v>1</v>
       </c>
       <c r="JB43" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35924,10 +35924,10 @@
         <v>1</v>
       </c>
       <c r="JB44" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.000356359406394884</v>
+        <v>-0.0001932167812876869</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.4586623150920038</v>
+        <v>0.2486850483800483</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36719,10 +36719,10 @@
         <v>0</v>
       </c>
       <c r="JB45" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.9181926399135468</v>
+        <v>0.4978407284960863</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.1059239810575001</v>
+        <v>-0.05743159942976306</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37514,10 +37514,10 @@
         <v>0</v>
       </c>
       <c r="JB46" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.1910602321689976</v>
       </c>
     </row>
     <row r="47">
@@ -38309,10 +38309,10 @@
         <v>1</v>
       </c>
       <c r="JB47" t="n">
-        <v>1.633306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.3523819746281088</v>
+        <v>0.1910602321689976</v>
       </c>
     </row>
     <row r="48">
@@ -39104,10 +39104,10 @@
         <v>1</v>
       </c>
       <c r="JB48" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.3519922083080998</v>
+        <v>0.1908596153485342</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>1.19744626729591</v>
+        <v>0.6163380974579478</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39899,10 +39899,10 @@
         <v>0</v>
       </c>
       <c r="JB49" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC49" t="n">
-        <v>2.749269463479246</v>
+        <v>1.424763408656399</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.2291178508372719</v>
+        <v>0.1179294123611085</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40694,10 +40694,10 @@
         <v>1</v>
       </c>
       <c r="JB50" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC50" t="n">
-        <v>2.008311258729316</v>
+        <v>1.043384386075021</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.4013216448407176</v>
+        <v>0.2065645499506417</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41489,10 +41489,10 @@
         <v>1</v>
       </c>
       <c r="JB51" t="n">
-        <v>1.633306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC51" t="n">
-        <v>2.581949320728867</v>
+        <v>1.338641881706236</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.219778575310485</v>
+        <v>0.1131220262980062</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42284,10 +42284,10 @@
         <v>0</v>
       </c>
       <c r="JB52" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC52" t="n">
-        <v>2.619838476051484</v>
+        <v>1.35814381515179</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.09077175230178069</v>
+        <v>0.0467210442896536</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43079,10 +43079,10 @@
         <v>1</v>
       </c>
       <c r="JB53" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC53" t="n">
-        <v>2.5813730088882</v>
+        <v>1.338345207261272</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.1130938138610675</v>
+        <v>0.05821090227510673</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43874,10 +43874,10 @@
         <v>1</v>
       </c>
       <c r="JB54" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC54" t="n">
-        <v>2.71680411994076</v>
+        <v>1.408053415883315</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.06809649394743847</v>
+        <v>0.03505048240960763</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44669,10 +44669,10 @@
         <v>1</v>
       </c>
       <c r="JB55" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC55" t="n">
-        <v>2.739827730757266</v>
+        <v>1.419903976557142</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.05177253967961519</v>
+        <v>0.0266477891912319</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45464,10 +45464,10 @@
         <v>0</v>
       </c>
       <c r="JB56" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC56" t="n">
-        <v>2.775246036014459</v>
+        <v>1.438134095030081</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.02289912903417543</v>
+        <v>0.01178436854233976</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46259,10 +46259,10 @@
         <v>1</v>
       </c>
       <c r="JB57" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC57" t="n">
-        <v>2.769226091984594</v>
+        <v>1.435034353698189</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.0181693706185043</v>
+        <v>0.009349883615358164</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47054,10 +47054,10 @@
         <v>1</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.633306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC58" t="n">
-        <v>2.782659980561601</v>
+        <v>1.441947290803425</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.009007833388688085</v>
+        <v>0.004635245888430862</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47849,10 +47849,10 @@
         <v>1</v>
       </c>
       <c r="JB59" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC59" t="n">
-        <v>2.782494103097988</v>
+        <v>1.441859473930881</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.005237379743624433</v>
+        <v>0.002691829091198584</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48644,10 +48644,10 @@
         <v>1</v>
       </c>
       <c r="JB60" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC60" t="n">
-        <v>2.783953766027672</v>
+        <v>1.44260834636753</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.002616189871812217</v>
+        <v>0.001344869145972107</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49439,10 +49439,10 @@
         <v>0</v>
       </c>
       <c r="JB61" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC61" t="n">
-        <v>2.783945502469337</v>
+        <v>1.442601665689319</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.001288591673071766</v>
+        <v>0.000661918373672555</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50234,10 +50234,10 @@
         <v>1</v>
       </c>
       <c r="JB62" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC62" t="n">
-        <v>2.783907721901414</v>
+        <v>1.442579783320591</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0007459718750281157</v>
+        <v>0.0003821677222367175</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51029,10 +51029,10 @@
         <v>0</v>
       </c>
       <c r="JB63" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC63" t="n">
-        <v>2.784110857057088</v>
+        <v>1.442681849565013</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0002472126228788256</v>
+        <v>0.0001244542666103707</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51824,10 +51824,10 @@
         <v>0</v>
       </c>
       <c r="JB64" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC64" t="n">
-        <v>2.783855355193342</v>
+        <v>1.442548273387161</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>0.0001207643042471784</v>
+        <v>6.012794327086025e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52619,10 +52619,10 @@
         <v>1</v>
       </c>
       <c r="JB65" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC65" t="n">
-        <v>2.783851760640701</v>
+        <v>1.442543994042195</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>6.349349164303817e-05</v>
+        <v>2.924674582151908e-05</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53414,10 +53414,10 @@
         <v>0</v>
       </c>
       <c r="JB66" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC66" t="n">
-        <v>2.783858111604302</v>
+        <v>1.442544769846875</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>2.818252625748566e-05</v>
+        <v>1.159126312874283e-05</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54209,10 +54209,10 @@
         <v>1</v>
       </c>
       <c r="JB67" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC67" t="n">
-        <v>2.783850862857269</v>
+        <v>1.442538607419853</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>1.536440521940679e-05</v>
+        <v>6.636802982518164e-06</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55004,10 +55004,10 @@
         <v>0</v>
       </c>
       <c r="JB68" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC68" t="n">
-        <v>2.783853932520712</v>
+        <v>1.442537910274449</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>5.309983785801169e-06</v>
+        <v>1.549918929005845e-07</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55799,10 +55799,10 @@
         <v>1</v>
       </c>
       <c r="JB69" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC69" t="n">
-        <v>2.783846262799617</v>
+        <v>1.442531575413901</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>9.151487243530285e-07</v>
+        <v>-2.042425637823487e-06</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56594,10 +56594,10 @@
         <v>1</v>
       </c>
       <c r="JB70" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC70" t="n">
-        <v>2.783842777579309</v>
+        <v>1.442527332803748</v>
       </c>
     </row>
     <row r="71">
@@ -57378,7 +57378,7 @@
         <v>0</v>
       </c>
       <c r="IY71" t="n">
-        <v>-1.814378588387752e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ71" t="inlineStr">
         <is>
@@ -57389,10 +57389,10 @@
         <v>0</v>
       </c>
       <c r="JB71" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC71" t="n">
-        <v>2.783838230267124</v>
+        <v>1.442527561124783</v>
       </c>
     </row>
     <row r="72">
@@ -58184,10 +58184,10 @@
         <v>0</v>
       </c>
       <c r="JB72" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC72" t="n">
-        <v>2.783838320211774</v>
+        <v>1.442527651069432</v>
       </c>
     </row>
     <row r="73">
@@ -58979,10 +58979,10 @@
         <v>1</v>
       </c>
       <c r="JB73" t="n">
-        <v>1.633306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC73" t="n">
-        <v>2.783837462278189</v>
+        <v>1.442526793135847</v>
       </c>
     </row>
     <row r="74">
@@ -59774,10 +59774,10 @@
         <v>0</v>
       </c>
       <c r="JB74" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC74" t="n">
-        <v>2.783837690599224</v>
+        <v>1.442527021456882</v>
       </c>
     </row>
     <row r="75">
@@ -60569,10 +60569,10 @@
         <v>0</v>
       </c>
       <c r="JB75" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC75" t="n">
-        <v>2.783836894935012</v>
+        <v>1.442526225792671</v>
       </c>
     </row>
     <row r="76">
@@ -61364,10 +61364,10 @@
         <v>0</v>
       </c>
       <c r="JB76" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC76" t="n">
-        <v>2.783836957204385</v>
+        <v>1.442526288062044</v>
       </c>
     </row>
     <row r="77">
@@ -62159,10 +62159,10 @@
         <v>1</v>
       </c>
       <c r="JB77" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC77" t="n">
-        <v>2.783836984879662</v>
+        <v>1.44252631573732</v>
       </c>
     </row>
     <row r="78">
@@ -62954,10 +62954,10 @@
         <v>1</v>
       </c>
       <c r="JB78" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC78" t="n">
-        <v>2.783837137093685</v>
+        <v>1.442526467951343</v>
       </c>
     </row>
     <row r="79">
@@ -63749,10 +63749,10 @@
         <v>0</v>
       </c>
       <c r="JB79" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC79" t="n">
-        <v>2.783836791152724</v>
+        <v>1.442526122010382</v>
       </c>
     </row>
     <row r="80">
@@ -64544,10 +64544,10 @@
         <v>1</v>
       </c>
       <c r="JB80" t="n">
-        <v>2.233306561630227</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC80" t="n">
-        <v>2.783836867259735</v>
+        <v>1.442526198117394</v>
       </c>
     </row>
     <row r="81">
@@ -65339,10 +65339,10 @@
         <v>0</v>
       </c>
       <c r="JB81" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC81" t="n">
-        <v>2.783837033311397</v>
+        <v>1.442526364169055</v>
       </c>
     </row>
     <row r="82">
@@ -66134,10 +66134,10 @@
         <v>1</v>
       </c>
       <c r="JB82" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC82" t="n">
-        <v>2.783837393089997</v>
+        <v>1.442526723947655</v>
       </c>
     </row>
     <row r="83">
@@ -66929,10 +66929,10 @@
         <v>1</v>
       </c>
       <c r="JB83" t="n">
-        <v>2.233306561630227</v>
+        <v>1.485695927975013</v>
       </c>
       <c r="JC83" t="n">
-        <v>2.783837413846455</v>
+        <v>1.442526744704113</v>
       </c>
     </row>
     <row r="84">
@@ -67724,10 +67724,10 @@
         <v>1</v>
       </c>
       <c r="JB84" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC84" t="n">
-        <v>2.783837517628743</v>
+        <v>1.442526848486401</v>
       </c>
     </row>
     <row r="85">
@@ -68519,10 +68519,10 @@
         <v>0</v>
       </c>
       <c r="JB85" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC85" t="n">
-        <v>2.783837745949778</v>
+        <v>1.442527076807436</v>
       </c>
     </row>
     <row r="86">
@@ -69314,10 +69314,10 @@
         <v>0</v>
       </c>
       <c r="JB86" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC86" t="n">
-        <v>2.783837621411032</v>
+        <v>1.44252695226869</v>
       </c>
     </row>
     <row r="87">
@@ -70109,10 +70109,10 @@
         <v>1</v>
       </c>
       <c r="JB87" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC87" t="n">
-        <v>2.783837649086309</v>
+        <v>1.442526979943967</v>
       </c>
     </row>
     <row r="88">
@@ -70904,10 +70904,10 @@
         <v>1</v>
       </c>
       <c r="JB88" t="n">
-        <v>2.233306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC88" t="n">
-        <v>2.783837704436862</v>
+        <v>1.442527035294521</v>
       </c>
     </row>
     <row r="89">
@@ -71699,10 +71699,10 @@
         <v>0</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC89" t="n">
-        <v>2.783837967351993</v>
+        <v>1.442527298209651</v>
       </c>
     </row>
     <row r="90">
@@ -72494,10 +72494,10 @@
         <v>0</v>
       </c>
       <c r="JB90" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC90" t="n">
-        <v>2.783837884326162</v>
+        <v>1.442527215183821</v>
       </c>
     </row>
     <row r="91">
@@ -73289,10 +73289,10 @@
         <v>1</v>
       </c>
       <c r="JB91" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC91" t="n">
-        <v>2.783837676761585</v>
+        <v>1.442527007619244</v>
       </c>
     </row>
     <row r="92">
@@ -74084,10 +74084,10 @@
         <v>1</v>
       </c>
       <c r="JB92" t="n">
-        <v>2.233306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC92" t="n">
-        <v>2.783837690599224</v>
+        <v>1.442527021456882</v>
       </c>
     </row>
     <row r="93">
@@ -74879,10 +74879,10 @@
         <v>0</v>
       </c>
       <c r="JB93" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC93" t="n">
-        <v>2.783837828975609</v>
+        <v>1.442527159833267</v>
       </c>
     </row>
     <row r="94">
@@ -75674,10 +75674,10 @@
         <v>0</v>
       </c>
       <c r="JB94" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC94" t="n">
-        <v>2.78383754530402</v>
+        <v>1.442526876161678</v>
       </c>
     </row>
     <row r="95">
@@ -76469,10 +76469,10 @@
         <v>0</v>
       </c>
       <c r="JB95" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC95" t="n">
-        <v>2.783837372333539</v>
+        <v>1.442526703191197</v>
       </c>
     </row>
     <row r="96">
@@ -77264,10 +77264,10 @@
         <v>1</v>
       </c>
       <c r="JB96" t="n">
-        <v>1.633306561630227</v>
+        <v>0.6120699483129129</v>
       </c>
       <c r="JC96" t="n">
-        <v>2.783837268551251</v>
+        <v>1.442526599408909</v>
       </c>
     </row>
     <row r="97">
@@ -78059,10 +78059,10 @@
         <v>1</v>
       </c>
       <c r="JB97" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC97" t="n">
-        <v>2.783837413846455</v>
+        <v>1.442526744704113</v>
       </c>
     </row>
     <row r="98">
@@ -78854,10 +78854,10 @@
         <v>0</v>
       </c>
       <c r="JB98" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC98" t="n">
-        <v>2.783837656005128</v>
+        <v>1.442526986862786</v>
       </c>
     </row>
     <row r="99">
@@ -79649,10 +79649,10 @@
         <v>0</v>
       </c>
       <c r="JB99" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC99" t="n">
-        <v>2.783837483034647</v>
+        <v>1.442526813892305</v>
       </c>
     </row>
     <row r="100">
@@ -80444,10 +80444,10 @@
         <v>0</v>
       </c>
       <c r="JB100" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC100" t="n">
-        <v>2.78383718552542</v>
+        <v>1.442526516383078</v>
       </c>
     </row>
     <row r="101">
@@ -81239,10 +81239,10 @@
         <v>0</v>
       </c>
       <c r="JB101" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC101" t="n">
-        <v>2.783837171687781</v>
+        <v>1.44252650254544</v>
       </c>
     </row>
     <row r="102">
@@ -82034,10 +82034,10 @@
         <v>0</v>
       </c>
       <c r="JB102" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC102" t="n">
-        <v>2.783836804990362</v>
+        <v>1.44252613584802</v>
       </c>
     </row>
     <row r="103">
@@ -82829,10 +82829,10 @@
         <v>1</v>
       </c>
       <c r="JB103" t="n">
-        <v>2.233306561630227</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC103" t="n">
-        <v>2.783836804990362</v>
+        <v>1.44252613584802</v>
       </c>
     </row>
     <row r="104">
@@ -83624,10 +83624,10 @@
         <v>0</v>
       </c>
       <c r="JB104" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC104" t="n">
-        <v>2.783836742720989</v>
+        <v>1.442526073578647</v>
       </c>
     </row>
     <row r="105">
@@ -84419,10 +84419,10 @@
         <v>0</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC105" t="n">
-        <v>2.7838366389387</v>
+        <v>1.442525969796359</v>
       </c>
     </row>
     <row r="106">
@@ -85214,10 +85214,10 @@
         <v>0</v>
       </c>
       <c r="JB106" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC106" t="n">
-        <v>2.78383646596822</v>
+        <v>1.442525796825878</v>
       </c>
     </row>
     <row r="107">
@@ -86009,10 +86009,10 @@
         <v>0</v>
       </c>
       <c r="JB107" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC107" t="n">
-        <v>2.783836514399954</v>
+        <v>1.442525845257612</v>
       </c>
     </row>
     <row r="108">
@@ -86804,10 +86804,10 @@
         <v>0</v>
       </c>
       <c r="JB108" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC108" t="n">
-        <v>2.783836154621354</v>
+        <v>1.442525485479013</v>
       </c>
     </row>
     <row r="109">
@@ -87599,10 +87599,10 @@
         <v>0</v>
       </c>
       <c r="JB109" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC109" t="n">
-        <v>2.783836113108439</v>
+        <v>1.442525443966097</v>
       </c>
     </row>
     <row r="110">
@@ -88394,10 +88394,10 @@
         <v>0</v>
       </c>
       <c r="JB110" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC110" t="n">
-        <v>2.783836168458993</v>
+        <v>1.442525499316651</v>
       </c>
     </row>
     <row r="111">
@@ -89189,10 +89189,10 @@
         <v>0</v>
       </c>
       <c r="JB111" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC111" t="n">
-        <v>2.783836223809547</v>
+        <v>1.442525554667205</v>
       </c>
     </row>
     <row r="112">
@@ -89984,10 +89984,10 @@
         <v>0</v>
       </c>
       <c r="JB112" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC112" t="n">
-        <v>2.783836265322462</v>
+        <v>1.44252559618012</v>
       </c>
     </row>
     <row r="113">
@@ -90779,10 +90779,10 @@
         <v>0</v>
       </c>
       <c r="JB113" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC113" t="n">
-        <v>2.783835995488512</v>
+        <v>1.44252532634617</v>
       </c>
     </row>
     <row r="114">
@@ -91574,10 +91574,10 @@
         <v>0</v>
       </c>
       <c r="JB114" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC114" t="n">
-        <v>2.783836050839065</v>
+        <v>1.442525381696724</v>
       </c>
     </row>
     <row r="115">
@@ -92369,10 +92369,10 @@
         <v>0</v>
       </c>
       <c r="JB115" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC115" t="n">
-        <v>2.78383619613427</v>
+        <v>1.442525526991928</v>
       </c>
     </row>
     <row r="116">
@@ -93164,10 +93164,10 @@
         <v>0</v>
       </c>
       <c r="JB116" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC116" t="n">
-        <v>2.783836161540174</v>
+        <v>1.442525492397832</v>
       </c>
     </row>
     <row r="117">
@@ -93959,10 +93959,10 @@
         <v>0</v>
       </c>
       <c r="JB117" t="n">
-        <v>-1.313807099391461</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC117" t="n">
-        <v>2.783836147702535</v>
+        <v>1.442525478560194</v>
       </c>
     </row>
     <row r="118">
@@ -94754,10 +94754,10 @@
         <v>1</v>
       </c>
       <c r="JB118" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC118" t="n">
-        <v>2.783836237647185</v>
+        <v>1.442525568504843</v>
       </c>
     </row>
     <row r="119">
@@ -95549,10 +95549,10 @@
         <v>1</v>
       </c>
       <c r="JB119" t="n">
-        <v>2.233306561630227</v>
+        <v>0.812069948312913</v>
       </c>
       <c r="JC119" t="n">
-        <v>2.783836555912869</v>
+        <v>1.442525886770528</v>
       </c>
     </row>
     <row r="120">
@@ -96344,10 +96344,10 @@
         <v>0</v>
       </c>
       <c r="JB120" t="n">
-        <v>-0.7138070993914605</v>
+        <v>0.1384439686508129</v>
       </c>
       <c r="JC120" t="n">
-        <v>2.78383637602357</v>
+        <v>1.442525706881228</v>
       </c>
     </row>
     <row r="121">
@@ -97139,10 +97139,10 @@
         <v>0</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.7138070993914605</v>
+        <v>-0.5351820110112873</v>
       </c>
       <c r="JC121" t="n">
-        <v>2.783836417536485</v>
+        <v>1.442525748394143</v>
       </c>
     </row>
     <row r="122">
@@ -97934,10 +97934,10 @@
         <v>0</v>
       </c>
       <c r="JB122" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC122" t="n">
-        <v>2.783836230728366</v>
+        <v>1.442525561586024</v>
       </c>
     </row>
     <row r="123">
@@ -98729,10 +98729,10 @@
         <v>0</v>
       </c>
       <c r="JB123" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC123" t="n">
-        <v>2.783836299916558</v>
+        <v>1.442525630774216</v>
       </c>
     </row>
     <row r="124">
@@ -99524,10 +99524,10 @@
         <v>0</v>
       </c>
       <c r="JB124" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.7351820110112873</v>
       </c>
       <c r="JC124" t="n">
-        <v>2.7838360992708</v>
+        <v>1.442525430128459</v>
       </c>
     </row>
     <row r="125">
@@ -100319,10 +100319,10 @@
         <v>0</v>
       </c>
       <c r="JB125" t="n">
-        <v>-1.313807099391461</v>
+        <v>-0.06155603134918715</v>
       </c>
       <c r="JC125" t="n">
-        <v>2.783836140783716</v>
+        <v>1.442525471641374</v>
       </c>
     </row>
     <row r="126">
@@ -101114,10 +101114,10 @@
         <v>1</v>
       </c>
       <c r="JB126" t="n">
-        <v>2.233306561630227</v>
+        <v>0.2752569584818629</v>
       </c>
       <c r="JC126" t="n">
-        <v>2.783836168458993</v>
+        <v>1.442525499316651</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000006.xlsx
@@ -1731,12 +1731,12 @@
       </c>
       <c r="JA1" s="1" t="inlineStr">
         <is>
-          <t>Predicted Value</t>
+          <t>Original Prediction</t>
         </is>
       </c>
       <c r="JB1" s="1" t="inlineStr">
         <is>
-          <t>Enhanced Signal</t>
+          <t>Trading Signal</t>
         </is>
       </c>
       <c r="JC1" s="1" t="inlineStr">
@@ -2531,10 +2531,10 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0</v>
+        <v>0.488022655248642</v>
       </c>
       <c r="JB2" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC2" t="n">
         <v>0</v>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0</v>
+        <v>0.4811038672924042</v>
       </c>
       <c r="JB3" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.2300000000000001</v>
       </c>
       <c r="JC3" t="n">
         <v>0</v>
@@ -4117,14 +4117,14 @@
       </c>
       <c r="IZ4" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA4" t="n">
-        <v>0</v>
+        <v>0.4836357533931732</v>
       </c>
       <c r="JB4" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.3</v>
       </c>
       <c r="JC4" t="n">
         <v>0</v>
@@ -4912,14 +4912,14 @@
       </c>
       <c r="IZ5" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA5" t="n">
-        <v>1</v>
+        <v>0.5074289441108704</v>
       </c>
       <c r="JB5" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC5" t="n">
         <v>0</v>
@@ -5711,10 +5711,10 @@
         </is>
       </c>
       <c r="JA6" t="n">
-        <v>0</v>
+        <v>0.4177467823028564</v>
       </c>
       <c r="JB6" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC6" t="n">
         <v>0</v>
@@ -6506,10 +6506,10 @@
         </is>
       </c>
       <c r="JA7" t="n">
-        <v>1</v>
+        <v>0.5009567737579346</v>
       </c>
       <c r="JB7" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC7" t="n">
         <v>0</v>
@@ -7297,14 +7297,14 @@
       </c>
       <c r="IZ8" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA8" t="n">
-        <v>0</v>
+        <v>0.4383847415447235</v>
       </c>
       <c r="JB8" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC8" t="n">
         <v>0</v>
@@ -8096,10 +8096,10 @@
         </is>
       </c>
       <c r="JA9" t="n">
-        <v>0</v>
+        <v>0.4722485244274139</v>
       </c>
       <c r="JB9" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC9" t="n">
         <v>0</v>
@@ -8891,10 +8891,10 @@
         </is>
       </c>
       <c r="JA10" t="n">
-        <v>0</v>
+        <v>0.4852086901664734</v>
       </c>
       <c r="JB10" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC10" t="n">
         <v>0</v>
@@ -9686,10 +9686,10 @@
         </is>
       </c>
       <c r="JA11" t="n">
-        <v>0</v>
+        <v>0.4057761132717133</v>
       </c>
       <c r="JB11" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC11" t="n">
         <v>0</v>
@@ -10481,10 +10481,10 @@
         </is>
       </c>
       <c r="JA12" t="n">
-        <v>0</v>
+        <v>0.47027388215065</v>
       </c>
       <c r="JB12" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC12" t="n">
         <v>0</v>
@@ -11276,10 +11276,10 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0</v>
+        <v>0.4486600756645203</v>
       </c>
       <c r="JB13" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC13" t="n">
         <v>0</v>
@@ -12071,10 +12071,10 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>1</v>
+        <v>0.5110042095184326</v>
       </c>
       <c r="JB14" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC14" t="n">
         <v>0</v>
@@ -12862,14 +12862,14 @@
       </c>
       <c r="IZ15" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0</v>
+        <v>0.4230601787567139</v>
       </c>
       <c r="JB15" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC15" t="n">
         <v>0</v>
@@ -13661,10 +13661,10 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0</v>
+        <v>0.4230552613735199</v>
       </c>
       <c r="JB16" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC16" t="n">
         <v>0</v>
@@ -14456,10 +14456,10 @@
         </is>
       </c>
       <c r="JA17" t="n">
-        <v>0</v>
+        <v>0.4227803349494934</v>
       </c>
       <c r="JB17" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC17" t="n">
         <v>0</v>
@@ -15247,14 +15247,14 @@
       </c>
       <c r="IZ18" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA18" t="n">
-        <v>0</v>
+        <v>0.483181357383728</v>
       </c>
       <c r="JB18" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.3</v>
       </c>
       <c r="JC18" t="n">
         <v>0</v>
@@ -16042,14 +16042,14 @@
       </c>
       <c r="IZ19" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0</v>
+        <v>0.4805429577827454</v>
       </c>
       <c r="JB19" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.3</v>
       </c>
       <c r="JC19" t="n">
         <v>0</v>
@@ -16841,10 +16841,10 @@
         </is>
       </c>
       <c r="JA20" t="n">
-        <v>1</v>
+        <v>0.5122847557067871</v>
       </c>
       <c r="JB20" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC20" t="n">
         <v>0</v>
@@ -17636,10 +17636,10 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0</v>
+        <v>0.4384163320064545</v>
       </c>
       <c r="JB21" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC21" t="n">
         <v>0</v>
@@ -18431,10 +18431,10 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0</v>
+        <v>0.3861115574836731</v>
       </c>
       <c r="JB22" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC22" t="n">
         <v>0</v>
@@ -19226,10 +19226,10 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0</v>
+        <v>0.4405272603034973</v>
       </c>
       <c r="JB23" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC23" t="n">
         <v>0</v>
@@ -20021,10 +20021,10 @@
         </is>
       </c>
       <c r="JA24" t="n">
-        <v>0</v>
+        <v>0.4242009520530701</v>
       </c>
       <c r="JB24" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC24" t="n">
         <v>0</v>
@@ -20812,14 +20812,14 @@
       </c>
       <c r="IZ25" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA25" t="n">
-        <v>1</v>
+        <v>0.5290435552597046</v>
       </c>
       <c r="JB25" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC25" t="n">
         <v>0</v>
@@ -21611,10 +21611,10 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0</v>
+        <v>0.3995951414108276</v>
       </c>
       <c r="JB26" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC26" t="n">
         <v>0</v>
@@ -22406,10 +22406,10 @@
         </is>
       </c>
       <c r="JA27" t="n">
-        <v>1</v>
+        <v>0.6172427535057068</v>
       </c>
       <c r="JB27" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC27" t="n">
         <v>0</v>
@@ -23201,10 +23201,10 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0</v>
+        <v>0.4622178077697754</v>
       </c>
       <c r="JB28" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC28" t="n">
         <v>0</v>
@@ -23992,14 +23992,14 @@
       </c>
       <c r="IZ29" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA29" t="n">
-        <v>0</v>
+        <v>0.4555004835128784</v>
       </c>
       <c r="JB29" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.3</v>
       </c>
       <c r="JC29" t="n">
         <v>0</v>
@@ -24787,14 +24787,14 @@
       </c>
       <c r="IZ30" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA30" t="n">
-        <v>0</v>
+        <v>0.3970944583415985</v>
       </c>
       <c r="JB30" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC30" t="n">
         <v>0</v>
@@ -25582,14 +25582,14 @@
       </c>
       <c r="IZ31" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA31" t="n">
-        <v>0</v>
+        <v>0.4820204079151154</v>
       </c>
       <c r="JB31" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC31" t="n">
         <v>0</v>
@@ -26381,10 +26381,10 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0</v>
+        <v>0.3958992660045624</v>
       </c>
       <c r="JB32" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC32" t="n">
         <v>0</v>
@@ -27176,10 +27176,10 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0</v>
+        <v>0.3876829147338867</v>
       </c>
       <c r="JB33" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC33" t="n">
         <v>0</v>
@@ -27971,10 +27971,10 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0</v>
+        <v>0.4406318366527557</v>
       </c>
       <c r="JB34" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC34" t="n">
         <v>0</v>
@@ -28762,14 +28762,14 @@
       </c>
       <c r="IZ35" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>1</v>
+        <v>0.505829393863678</v>
       </c>
       <c r="JB35" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC35" t="n">
         <v>0</v>
@@ -29557,14 +29557,14 @@
       </c>
       <c r="IZ36" t="inlineStr">
         <is>
-          <t>Sell</t>
+          <t>Hold</t>
         </is>
       </c>
       <c r="JA36" t="n">
-        <v>0</v>
+        <v>0.4140713214874268</v>
       </c>
       <c r="JB36" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC36" t="n">
         <v>0</v>
@@ -30352,14 +30352,14 @@
       </c>
       <c r="IZ37" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA37" t="n">
-        <v>0</v>
+        <v>0.4081832468509674</v>
       </c>
       <c r="JB37" t="n">
-        <v>-0.5351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC37" t="n">
         <v>0</v>
@@ -31147,14 +31147,14 @@
       </c>
       <c r="IZ38" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA38" t="n">
-        <v>0</v>
+        <v>0.4922478199005127</v>
       </c>
       <c r="JB38" t="n">
-        <v>-0.5351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC38" t="n">
         <v>0</v>
@@ -31946,10 +31946,10 @@
         </is>
       </c>
       <c r="JA39" t="n">
-        <v>0</v>
+        <v>0.3798488676548004</v>
       </c>
       <c r="JB39" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC39" t="n">
         <v>0</v>
@@ -32741,10 +32741,10 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0</v>
+        <v>0.4112935364246368</v>
       </c>
       <c r="JB40" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC40" t="n">
         <v>0</v>
@@ -33532,14 +33532,14 @@
       </c>
       <c r="IZ41" t="inlineStr">
         <is>
-          <t>Hold</t>
+          <t>Sell</t>
         </is>
       </c>
       <c r="JA41" t="n">
-        <v>0</v>
+        <v>0.4317242801189423</v>
       </c>
       <c r="JB41" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.16</v>
       </c>
       <c r="JC41" t="n">
         <v>0</v>
@@ -34331,10 +34331,10 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>1</v>
+        <v>0.5498231649398804</v>
       </c>
       <c r="JB42" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC42" t="n">
         <v>0</v>
@@ -35126,10 +35126,10 @@
         </is>
       </c>
       <c r="JA43" t="n">
-        <v>1</v>
+        <v>0.6128669381141663</v>
       </c>
       <c r="JB43" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC43" t="n">
         <v>0</v>
@@ -35921,13 +35921,13 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>1</v>
+        <v>0.5997248291969299</v>
       </c>
       <c r="JB44" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC44" t="n">
-        <v>-0.0001932167812876869</v>
+        <v>-0.0001505071560592624</v>
       </c>
     </row>
     <row r="45">
@@ -36708,7 +36708,7 @@
         <v>0</v>
       </c>
       <c r="IY45" t="n">
-        <v>0.2486850483800483</v>
+        <v>0.1937144337915407</v>
       </c>
       <c r="IZ45" t="inlineStr">
         <is>
@@ -36716,13 +36716,13 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0</v>
+        <v>0.3964666426181793</v>
       </c>
       <c r="JB45" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC45" t="n">
-        <v>0.4978407284960863</v>
+        <v>0.3877954684738684</v>
       </c>
     </row>
     <row r="46">
@@ -37503,7 +37503,7 @@
         <v>0</v>
       </c>
       <c r="IY46" t="n">
-        <v>-0.05743159942976306</v>
+        <v>-0.04473662505144678</v>
       </c>
       <c r="IZ46" t="inlineStr">
         <is>
@@ -37511,13 +37511,13 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0</v>
+        <v>0.2556702494621277</v>
       </c>
       <c r="JB46" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC46" t="n">
-        <v>0.1910602321689976</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="47">
@@ -38306,13 +38306,13 @@
         </is>
       </c>
       <c r="JA47" t="n">
-        <v>1</v>
+        <v>0.5802449584007263</v>
       </c>
       <c r="JB47" t="n">
-        <v>0.812069948312913</v>
+        <v>0.02000000000000007</v>
       </c>
       <c r="JC47" t="n">
-        <v>0.1910602321689976</v>
+        <v>0.1488273015840347</v>
       </c>
     </row>
     <row r="48">
@@ -39101,13 +39101,13 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>1</v>
+        <v>0.6000362038612366</v>
       </c>
       <c r="JB48" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.3</v>
       </c>
       <c r="JC48" t="n">
-        <v>0.1908596153485342</v>
+        <v>0.1487414633451898</v>
       </c>
     </row>
     <row r="49">
@@ -39888,7 +39888,7 @@
         <v>0</v>
       </c>
       <c r="IY49" t="n">
-        <v>0.6163380974579478</v>
+        <v>0.2637136339091658</v>
       </c>
       <c r="IZ49" t="inlineStr">
         <is>
@@ -39896,13 +39896,13 @@
         </is>
       </c>
       <c r="JA49" t="n">
-        <v>0</v>
+        <v>0.3780640959739685</v>
       </c>
       <c r="JB49" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC49" t="n">
-        <v>1.424763408656399</v>
+        <v>0.6766938466458761</v>
       </c>
     </row>
     <row r="50">
@@ -40683,7 +40683,7 @@
         <v>0</v>
       </c>
       <c r="IY50" t="n">
-        <v>0.1179294123611085</v>
+        <v>0.05045857031788842</v>
       </c>
       <c r="IZ50" t="inlineStr">
         <is>
@@ -40691,13 +40691,13 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>1</v>
+        <v>0.6309744119644165</v>
       </c>
       <c r="JB50" t="n">
-        <v>0.812069948312913</v>
+        <v>0.3</v>
       </c>
       <c r="JC50" t="n">
-        <v>1.043384386075021</v>
+        <v>0.5135126392995678</v>
       </c>
     </row>
     <row r="51">
@@ -41478,7 +41478,7 @@
         <v>0</v>
       </c>
       <c r="IY51" t="n">
-        <v>0.2065645499506417</v>
+        <v>0.08838297130618772</v>
       </c>
       <c r="IZ51" t="inlineStr">
         <is>
@@ -41486,13 +41486,13 @@
         </is>
       </c>
       <c r="JA51" t="n">
-        <v>1</v>
+        <v>0.5137948393821716</v>
       </c>
       <c r="JB51" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC51" t="n">
-        <v>1.338641881706236</v>
+        <v>0.6398450573440544</v>
       </c>
     </row>
     <row r="52">
@@ -42273,7 +42273,7 @@
         <v>0</v>
       </c>
       <c r="IY52" t="n">
-        <v>0.1131220262980062</v>
+        <v>0.0484019696582307</v>
       </c>
       <c r="IZ52" t="inlineStr">
         <is>
@@ -42281,13 +42281,13 @@
         </is>
       </c>
       <c r="JA52" t="n">
-        <v>0</v>
+        <v>0.4281098246574402</v>
       </c>
       <c r="JB52" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC52" t="n">
-        <v>1.35814381515179</v>
+        <v>0.6481894091249795</v>
       </c>
     </row>
     <row r="53">
@@ -43068,7 +43068,7 @@
         <v>0</v>
       </c>
       <c r="IY53" t="n">
-        <v>0.0467210442896536</v>
+        <v>0.01999052154930155</v>
       </c>
       <c r="IZ53" t="inlineStr">
         <is>
@@ -43076,13 +43076,13 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>1</v>
+        <v>0.6636998653411865</v>
       </c>
       <c r="JB53" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC53" t="n">
-        <v>1.338345207261272</v>
+        <v>0.639718136210965</v>
       </c>
     </row>
     <row r="54">
@@ -43863,7 +43863,7 @@
         <v>0</v>
       </c>
       <c r="IY54" t="n">
-        <v>0.05821090227510673</v>
+        <v>0.02490647437945315</v>
       </c>
       <c r="IZ54" t="inlineStr">
         <is>
@@ -43871,13 +43871,13 @@
         </is>
       </c>
       <c r="JA54" t="n">
-        <v>1</v>
+        <v>0.6811843514442444</v>
       </c>
       <c r="JB54" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC54" t="n">
-        <v>1.408053415883315</v>
+        <v>0.6695445068397418</v>
       </c>
     </row>
     <row r="55">
@@ -44658,7 +44658,7 @@
         <v>0</v>
       </c>
       <c r="IY55" t="n">
-        <v>0.03505048240960763</v>
+        <v>0.01499741439236807</v>
       </c>
       <c r="IZ55" t="inlineStr">
         <is>
@@ -44666,13 +44666,13 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>1</v>
+        <v>0.7229295372962952</v>
       </c>
       <c r="JB55" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC55" t="n">
-        <v>1.419903976557142</v>
+        <v>0.6746150692310582</v>
       </c>
     </row>
     <row r="56">
@@ -45453,7 +45453,7 @@
         <v>0</v>
       </c>
       <c r="IY56" t="n">
-        <v>0.0266477891912319</v>
+        <v>0.01139986482293197</v>
       </c>
       <c r="IZ56" t="inlineStr">
         <is>
@@ -45461,13 +45461,13 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0</v>
+        <v>0.435119092464447</v>
       </c>
       <c r="JB56" t="n">
-        <v>0.812069948312913</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC56" t="n">
-        <v>1.438134095030081</v>
+        <v>0.6824140553408168</v>
       </c>
     </row>
     <row r="57">
@@ -46248,7 +46248,7 @@
         <v>0</v>
       </c>
       <c r="IY57" t="n">
-        <v>0.01178436854233976</v>
+        <v>0.005039413016094149</v>
       </c>
       <c r="IZ57" t="inlineStr">
         <is>
@@ -46256,13 +46256,13 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>1</v>
+        <v>0.6981275677680969</v>
       </c>
       <c r="JB57" t="n">
-        <v>0.6120699483129129</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC57" t="n">
-        <v>1.435034353698189</v>
+        <v>0.6810847644414517</v>
       </c>
     </row>
     <row r="58">
@@ -47043,7 +47043,7 @@
         <v>0</v>
       </c>
       <c r="IY58" t="n">
-        <v>0.009349883615358164</v>
+        <v>0.003997750147633703</v>
       </c>
       <c r="IZ58" t="inlineStr">
         <is>
@@ -47051,13 +47051,13 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>1</v>
+        <v>0.6515438556671143</v>
       </c>
       <c r="JB58" t="n">
-        <v>1.485695927975013</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC58" t="n">
-        <v>1.441947290803425</v>
+        <v>0.6840403328480719</v>
       </c>
     </row>
     <row r="59">
@@ -47838,7 +47838,7 @@
         <v>0</v>
       </c>
       <c r="IY59" t="n">
-        <v>0.004635245888430862</v>
+        <v>0.001981175329064207</v>
       </c>
       <c r="IZ59" t="inlineStr">
         <is>
@@ -47846,13 +47846,13 @@
         </is>
       </c>
       <c r="JA59" t="n">
-        <v>1</v>
+        <v>0.8125277757644653</v>
       </c>
       <c r="JB59" t="n">
-        <v>1.485695927975013</v>
+        <v>0.5799999999999998</v>
       </c>
       <c r="JC59" t="n">
-        <v>1.441859473930881</v>
+        <v>0.6839998845479104</v>
       </c>
     </row>
     <row r="60">
@@ -48633,7 +48633,7 @@
         <v>0</v>
       </c>
       <c r="IY60" t="n">
-        <v>0.002691829091198584</v>
+        <v>0.001149952696014928</v>
       </c>
       <c r="IZ60" t="inlineStr">
         <is>
@@ -48641,13 +48641,13 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>1</v>
+        <v>0.8129528164863586</v>
       </c>
       <c r="JB60" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC60" t="n">
-        <v>1.44260834636753</v>
+        <v>0.6843175655596112</v>
       </c>
     </row>
     <row r="61">
@@ -49428,7 +49428,7 @@
         <v>0</v>
       </c>
       <c r="IY61" t="n">
-        <v>0.001344869145972107</v>
+        <v>0.0005710217476346492</v>
       </c>
       <c r="IZ61" t="inlineStr">
         <is>
@@ -49436,13 +49436,13 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0</v>
+        <v>0.224351242184639</v>
       </c>
       <c r="JB61" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC61" t="n">
-        <v>1.442601665689319</v>
+        <v>0.6843118483736508</v>
       </c>
     </row>
     <row r="62">
@@ -50223,7 +50223,7 @@
         <v>0</v>
       </c>
       <c r="IY62" t="n">
-        <v>0.000661918373672555</v>
+        <v>0.0002795901680757886</v>
       </c>
       <c r="IZ62" t="inlineStr">
         <is>
@@ -50231,13 +50231,13 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>1</v>
+        <v>0.7652610540390015</v>
       </c>
       <c r="JB62" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC62" t="n">
-        <v>1.442579783320591</v>
+        <v>0.6842996096653126</v>
       </c>
     </row>
     <row r="63">
@@ -51018,7 +51018,7 @@
         <v>0</v>
       </c>
       <c r="IY63" t="n">
-        <v>0.0003821677222367175</v>
+        <v>0.0001618826388951368</v>
       </c>
       <c r="IZ63" t="inlineStr">
         <is>
@@ -51026,13 +51026,13 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0</v>
+        <v>0.1902934163808823</v>
       </c>
       <c r="JB63" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC63" t="n">
-        <v>1.442681849565013</v>
+        <v>0.684340758908598</v>
       </c>
     </row>
     <row r="64">
@@ -51813,7 +51813,7 @@
         <v>0</v>
       </c>
       <c r="IY64" t="n">
-        <v>0.0001244542666103707</v>
+        <v>5.079925284929769e-05</v>
       </c>
       <c r="IZ64" t="inlineStr">
         <is>
@@ -51821,13 +51821,13 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0</v>
+        <v>0.4603838324546814</v>
       </c>
       <c r="JB64" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC64" t="n">
-        <v>1.442548273387161</v>
+        <v>0.6842803381422825</v>
       </c>
     </row>
     <row r="65">
@@ -52608,7 +52608,7 @@
         <v>0</v>
       </c>
       <c r="IY65" t="n">
-        <v>6.012794327086025e-05</v>
+        <v>2.194949376725252e-05</v>
       </c>
       <c r="IZ65" t="inlineStr">
         <is>
@@ -52616,13 +52616,13 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>1</v>
+        <v>0.5649556517601013</v>
       </c>
       <c r="JB65" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC65" t="n">
-        <v>1.442543994042195</v>
+        <v>0.6842756501820041</v>
       </c>
     </row>
     <row r="66">
@@ -53403,7 +53403,7 @@
         <v>0</v>
       </c>
       <c r="IY66" t="n">
-        <v>2.924674582151908e-05</v>
+        <v>9.677176780651038e-06</v>
       </c>
       <c r="IZ66" t="inlineStr">
         <is>
@@ -53411,13 +53411,13 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0</v>
+        <v>0.4356594085693359</v>
       </c>
       <c r="JB66" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC66" t="n">
-        <v>1.442544769846875</v>
+        <v>0.6842732401815853</v>
       </c>
     </row>
     <row r="67">
@@ -54198,7 +54198,7 @@
         <v>0</v>
       </c>
       <c r="IY67" t="n">
-        <v>1.159126312874283e-05</v>
+        <v>2.110541340889784e-06</v>
       </c>
       <c r="IZ67" t="inlineStr">
         <is>
@@ -54206,13 +54206,13 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>1</v>
+        <v>0.8058984875679016</v>
       </c>
       <c r="JB67" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.3</v>
       </c>
       <c r="JC67" t="n">
-        <v>1.442538607419853</v>
+        <v>0.6842676985088549</v>
       </c>
     </row>
     <row r="68">
@@ -54993,7 +54993,7 @@
         <v>0</v>
       </c>
       <c r="IY68" t="n">
-        <v>6.636802982518164e-06</v>
+        <v>8.184014912590811e-07</v>
       </c>
       <c r="IZ68" t="inlineStr">
         <is>
@@ -55001,13 +55001,13 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0</v>
+        <v>0.3907082676887512</v>
       </c>
       <c r="JB68" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.1600000000000001</v>
       </c>
       <c r="JC68" t="n">
-        <v>1.442537910274449</v>
+        <v>0.684264849936153</v>
       </c>
     </row>
     <row r="69">
@@ -55788,7 +55788,7 @@
         <v>0</v>
       </c>
       <c r="IY69" t="n">
-        <v>1.549918929005845e-07</v>
+        <v>-2.422504053549707e-06</v>
       </c>
       <c r="IZ69" t="inlineStr">
         <is>
@@ -55796,13 +55796,13 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>1</v>
+        <v>0.7346447110176086</v>
       </c>
       <c r="JB69" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC69" t="n">
-        <v>1.442531575413901</v>
+        <v>0.6842591825058794</v>
       </c>
     </row>
     <row r="70">
@@ -56583,7 +56583,7 @@
         <v>0</v>
       </c>
       <c r="IY70" t="n">
-        <v>-2.042425637823487e-06</v>
+        <v>0</v>
       </c>
       <c r="IZ70" t="inlineStr">
         <is>
@@ -56591,13 +56591,13 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>1</v>
+        <v>0.7675833106040955</v>
       </c>
       <c r="JB70" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC70" t="n">
-        <v>1.442527332803748</v>
+        <v>0.684259563040937</v>
       </c>
     </row>
     <row r="71">
@@ -57386,13 +57386,13 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0</v>
+        <v>0.3728429973125458</v>
       </c>
       <c r="JB71" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC71" t="n">
-        <v>1.442527561124783</v>
+        <v>0.6842597913619718</v>
       </c>
     </row>
     <row r="72">
@@ -58181,13 +58181,13 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0</v>
+        <v>0.16764797270298</v>
       </c>
       <c r="JB72" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC72" t="n">
-        <v>1.442527651069432</v>
+        <v>0.6842598813066217</v>
       </c>
     </row>
     <row r="73">
@@ -58976,13 +58976,13 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>1</v>
+        <v>0.5131186246871948</v>
       </c>
       <c r="JB73" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC73" t="n">
-        <v>1.442526793135847</v>
+        <v>0.6842590233730369</v>
       </c>
     </row>
     <row r="74">
@@ -59771,13 +59771,13 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0</v>
+        <v>0.2291493117809296</v>
       </c>
       <c r="JB74" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC74" t="n">
-        <v>1.442527021456882</v>
+        <v>0.6842592516940715</v>
       </c>
     </row>
     <row r="75">
@@ -60566,13 +60566,13 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0</v>
+        <v>0.4852877855300903</v>
       </c>
       <c r="JB75" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.8599999999999999</v>
       </c>
       <c r="JC75" t="n">
-        <v>1.442526225792671</v>
+        <v>0.6842584560298598</v>
       </c>
     </row>
     <row r="76">
@@ -61361,13 +61361,13 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0</v>
+        <v>0.4039653837680817</v>
       </c>
       <c r="JB76" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC76" t="n">
-        <v>1.442526288062044</v>
+        <v>0.6842585182992329</v>
       </c>
     </row>
     <row r="77">
@@ -62156,13 +62156,13 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>1</v>
+        <v>0.5301371216773987</v>
       </c>
       <c r="JB77" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC77" t="n">
-        <v>1.44252631573732</v>
+        <v>0.6842585459745097</v>
       </c>
     </row>
     <row r="78">
@@ -62951,13 +62951,13 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>1</v>
+        <v>0.5338163375854492</v>
       </c>
       <c r="JB78" t="n">
-        <v>0.812069948312913</v>
+        <v>0.16</v>
       </c>
       <c r="JC78" t="n">
-        <v>1.442526467951343</v>
+        <v>0.684258698188533</v>
       </c>
     </row>
     <row r="79">
@@ -63746,13 +63746,13 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0</v>
+        <v>0.393704354763031</v>
       </c>
       <c r="JB79" t="n">
-        <v>0.812069948312913</v>
+        <v>0.16</v>
       </c>
       <c r="JC79" t="n">
-        <v>1.442526122010382</v>
+        <v>0.6842583522475714</v>
       </c>
     </row>
     <row r="80">
@@ -64541,13 +64541,13 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>1</v>
+        <v>0.6042994260787964</v>
       </c>
       <c r="JB80" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.3</v>
       </c>
       <c r="JC80" t="n">
-        <v>1.442526198117394</v>
+        <v>0.6842584283545829</v>
       </c>
     </row>
     <row r="81">
@@ -65336,13 +65336,13 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0</v>
+        <v>0.4034383893013</v>
       </c>
       <c r="JB81" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC81" t="n">
-        <v>1.442526364169055</v>
+        <v>0.6842585944062446</v>
       </c>
     </row>
     <row r="82">
@@ -66131,13 +66131,13 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>1</v>
+        <v>0.7514288425445557</v>
       </c>
       <c r="JB82" t="n">
-        <v>0.812069948312913</v>
+        <v>0.7199999999999999</v>
       </c>
       <c r="JC82" t="n">
-        <v>1.442526723947655</v>
+        <v>0.6842589541848446</v>
       </c>
     </row>
     <row r="83">
@@ -66926,13 +66926,13 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>1</v>
+        <v>0.5877249240875244</v>
       </c>
       <c r="JB83" t="n">
-        <v>1.485695927975013</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC83" t="n">
-        <v>1.442526744704113</v>
+        <v>0.6842589749413023</v>
       </c>
     </row>
     <row r="84">
@@ -67721,13 +67721,13 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>1</v>
+        <v>0.7363027334213257</v>
       </c>
       <c r="JB84" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC84" t="n">
-        <v>1.442526848486401</v>
+        <v>0.6842590787235908</v>
       </c>
     </row>
     <row r="85">
@@ -68516,13 +68516,13 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0</v>
+        <v>0.4857492744922638</v>
       </c>
       <c r="JB85" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC85" t="n">
-        <v>1.442527076807436</v>
+        <v>0.6842593070446256</v>
       </c>
     </row>
     <row r="86">
@@ -69311,13 +69311,13 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0</v>
+        <v>0.4740878045558929</v>
       </c>
       <c r="JB86" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC86" t="n">
-        <v>1.44252695226869</v>
+        <v>0.6842591825058794</v>
       </c>
     </row>
     <row r="87">
@@ -70106,13 +70106,13 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>1</v>
+        <v>0.5162799954414368</v>
       </c>
       <c r="JB87" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC87" t="n">
-        <v>1.442526979943967</v>
+        <v>0.6842592101811562</v>
       </c>
     </row>
     <row r="88">
@@ -70901,13 +70901,13 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>1</v>
+        <v>0.7422133684158325</v>
       </c>
       <c r="JB88" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC88" t="n">
-        <v>1.442527035294521</v>
+        <v>0.6842592655317101</v>
       </c>
     </row>
     <row r="89">
@@ -71696,13 +71696,13 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0</v>
+        <v>0.3018356263637543</v>
       </c>
       <c r="JB89" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.3</v>
       </c>
       <c r="JC89" t="n">
-        <v>1.442527298209651</v>
+        <v>0.6842595284468408</v>
       </c>
     </row>
     <row r="90">
@@ -72491,13 +72491,13 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0</v>
+        <v>0.4955836832523346</v>
       </c>
       <c r="JB90" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.02000000000000007</v>
       </c>
       <c r="JC90" t="n">
-        <v>1.442527215183821</v>
+        <v>0.68425944542101</v>
       </c>
     </row>
     <row r="91">
@@ -73286,13 +73286,13 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>1</v>
+        <v>0.5621458888053894</v>
       </c>
       <c r="JB91" t="n">
-        <v>0.6120699483129129</v>
+        <v>0.3</v>
       </c>
       <c r="JC91" t="n">
-        <v>1.442527007619244</v>
+        <v>0.6842592378564333</v>
       </c>
     </row>
     <row r="92">
@@ -74081,13 +74081,13 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>1</v>
+        <v>0.5481483936309814</v>
       </c>
       <c r="JB92" t="n">
-        <v>0.6120699483129129</v>
+        <v>0.3</v>
       </c>
       <c r="JC92" t="n">
-        <v>1.442527021456882</v>
+        <v>0.6842592516940715</v>
       </c>
     </row>
     <row r="93">
@@ -74876,13 +74876,13 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0</v>
+        <v>0.3974269330501556</v>
       </c>
       <c r="JB93" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.16</v>
       </c>
       <c r="JC93" t="n">
-        <v>1.442527159833267</v>
+        <v>0.6842593900704563</v>
       </c>
     </row>
     <row r="94">
@@ -75671,13 +75671,13 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0</v>
+        <v>0.3201610147953033</v>
       </c>
       <c r="JB94" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC94" t="n">
-        <v>1.442526876161678</v>
+        <v>0.6842591063988677</v>
       </c>
     </row>
     <row r="95">
@@ -76466,13 +76466,13 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0</v>
+        <v>0.3741748034954071</v>
       </c>
       <c r="JB95" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC95" t="n">
-        <v>1.442526703191197</v>
+        <v>0.684258933428387</v>
       </c>
     </row>
     <row r="96">
@@ -77261,13 +77261,13 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>1</v>
+        <v>0.6763342022895813</v>
       </c>
       <c r="JB96" t="n">
-        <v>0.6120699483129129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC96" t="n">
-        <v>1.442526599408909</v>
+        <v>0.6842588296460984</v>
       </c>
     </row>
     <row r="97">
@@ -78056,13 +78056,13 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>1</v>
+        <v>0.6145511269569397</v>
       </c>
       <c r="JB97" t="n">
-        <v>0.812069948312913</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC97" t="n">
-        <v>1.442526744704113</v>
+        <v>0.6842589749413023</v>
       </c>
     </row>
     <row r="98">
@@ -78851,13 +78851,13 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0</v>
+        <v>0.4709202945232391</v>
       </c>
       <c r="JB98" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC98" t="n">
-        <v>1.442526986862786</v>
+        <v>0.6842592170999756</v>
       </c>
     </row>
     <row r="99">
@@ -79646,13 +79646,13 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0</v>
+        <v>0.2231430560350418</v>
       </c>
       <c r="JB99" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC99" t="n">
-        <v>1.442526813892305</v>
+        <v>0.6842590441294946</v>
       </c>
     </row>
     <row r="100">
@@ -80441,13 +80441,13 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0</v>
+        <v>0.4341157674789429</v>
       </c>
       <c r="JB100" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC100" t="n">
-        <v>1.442526516383078</v>
+        <v>0.6842587466202676</v>
       </c>
     </row>
     <row r="101">
@@ -81236,13 +81236,13 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0</v>
+        <v>0.2131999582052231</v>
       </c>
       <c r="JB101" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC101" t="n">
-        <v>1.44252650254544</v>
+        <v>0.6842587327826291</v>
       </c>
     </row>
     <row r="102">
@@ -82031,13 +82031,13 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0</v>
+        <v>0.4170821309089661</v>
       </c>
       <c r="JB102" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC102" t="n">
-        <v>1.44252613584802</v>
+        <v>0.6842583660852098</v>
       </c>
     </row>
     <row r="103">
@@ -82826,13 +82826,13 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>1</v>
+        <v>0.6004751920700073</v>
       </c>
       <c r="JB103" t="n">
-        <v>-0.06155603134918715</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC103" t="n">
-        <v>1.44252613584802</v>
+        <v>0.6842583660852098</v>
       </c>
     </row>
     <row r="104">
@@ -83621,13 +83621,13 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0</v>
+        <v>0.2639464437961578</v>
       </c>
       <c r="JB104" t="n">
-        <v>0.1384439686508129</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC104" t="n">
-        <v>1.442526073578647</v>
+        <v>0.6842583038158367</v>
       </c>
     </row>
     <row r="105">
@@ -84416,13 +84416,13 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0</v>
+        <v>0.3377128541469574</v>
       </c>
       <c r="JB105" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC105" t="n">
-        <v>1.442525969796359</v>
+        <v>0.6842582000335483</v>
       </c>
     </row>
     <row r="106">
@@ -85211,13 +85211,13 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0</v>
+        <v>0.4114673435688019</v>
       </c>
       <c r="JB106" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC106" t="n">
-        <v>1.442525796825878</v>
+        <v>0.6842580270630675</v>
       </c>
     </row>
     <row r="107">
@@ -86006,13 +86006,13 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0</v>
+        <v>0.2656219303607941</v>
       </c>
       <c r="JB107" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.9999999999999998</v>
       </c>
       <c r="JC107" t="n">
-        <v>1.442525845257612</v>
+        <v>0.6842580754948021</v>
       </c>
     </row>
     <row r="108">
@@ -86801,13 +86801,13 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0</v>
+        <v>0.2876636385917664</v>
       </c>
       <c r="JB108" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC108" t="n">
-        <v>1.442525485479013</v>
+        <v>0.6842577157162021</v>
       </c>
     </row>
     <row r="109">
@@ -87596,13 +87596,13 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0</v>
+        <v>0.4344042241573334</v>
       </c>
       <c r="JB109" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.7199999999999999</v>
       </c>
       <c r="JC109" t="n">
-        <v>1.442525443966097</v>
+        <v>0.6842576742032866</v>
       </c>
     </row>
     <row r="110">
@@ -88391,13 +88391,13 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0</v>
+        <v>0.4746588468551636</v>
       </c>
       <c r="JB110" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC110" t="n">
-        <v>1.442525499316651</v>
+        <v>0.6842577295538403</v>
       </c>
     </row>
     <row r="111">
@@ -89186,13 +89186,13 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0</v>
+        <v>0.3380211591720581</v>
       </c>
       <c r="JB111" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC111" t="n">
-        <v>1.442525554667205</v>
+        <v>0.6842577849043943</v>
       </c>
     </row>
     <row r="112">
@@ -89981,13 +89981,13 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0</v>
+        <v>0.2806555330753326</v>
       </c>
       <c r="JB112" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC112" t="n">
-        <v>1.44252559618012</v>
+        <v>0.6842578264173097</v>
       </c>
     </row>
     <row r="113">
@@ -90776,13 +90776,13 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0</v>
+        <v>0.3019035160541534</v>
       </c>
       <c r="JB113" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.1199999999999999</v>
       </c>
       <c r="JC113" t="n">
-        <v>1.44252532634617</v>
+        <v>0.6842575565833596</v>
       </c>
     </row>
     <row r="114">
@@ -91571,13 +91571,13 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0</v>
+        <v>0.487054854631424</v>
       </c>
       <c r="JB114" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC114" t="n">
-        <v>1.442525381696724</v>
+        <v>0.6842576119339135</v>
       </c>
     </row>
     <row r="115">
@@ -92366,13 +92366,13 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0</v>
+        <v>0.3261367082595825</v>
       </c>
       <c r="JB115" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC115" t="n">
-        <v>1.442525526991928</v>
+        <v>0.6842577572291174</v>
       </c>
     </row>
     <row r="116">
@@ -93161,13 +93161,13 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0</v>
+        <v>0.4251779615879059</v>
       </c>
       <c r="JB116" t="n">
-        <v>-0.7351820110112873</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC116" t="n">
-        <v>1.442525492397832</v>
+        <v>0.6842577226350212</v>
       </c>
     </row>
     <row r="117">
@@ -93956,13 +93956,13 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0</v>
+        <v>0.3146539032459259</v>
       </c>
       <c r="JB117" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC117" t="n">
-        <v>1.442525478560194</v>
+        <v>0.6842577087973827</v>
       </c>
     </row>
     <row r="118">
@@ -94751,13 +94751,13 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>1</v>
+        <v>0.7171016931533813</v>
       </c>
       <c r="JB118" t="n">
-        <v>0.812069948312913</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC118" t="n">
-        <v>1.442525568504843</v>
+        <v>0.6842577987420329</v>
       </c>
     </row>
     <row r="119">
@@ -95546,13 +95546,13 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>1</v>
+        <v>0.6038730144500732</v>
       </c>
       <c r="JB119" t="n">
-        <v>0.812069948312913</v>
+        <v>0.1600000000000001</v>
       </c>
       <c r="JC119" t="n">
-        <v>1.442525886770528</v>
+        <v>0.6842581170077174</v>
       </c>
     </row>
     <row r="120">
@@ -96341,13 +96341,13 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0</v>
+        <v>0.2751888334751129</v>
       </c>
       <c r="JB120" t="n">
-        <v>0.1384439686508129</v>
+        <v>0.4399999999999999</v>
       </c>
       <c r="JC120" t="n">
-        <v>1.442525706881228</v>
+        <v>0.6842579371184173</v>
       </c>
     </row>
     <row r="121">
@@ -97136,13 +97136,13 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0</v>
+        <v>0.351144939661026</v>
       </c>
       <c r="JB121" t="n">
-        <v>-0.5351820110112873</v>
+        <v>0.16</v>
       </c>
       <c r="JC121" t="n">
-        <v>1.442525748394143</v>
+        <v>0.6842579786313328</v>
       </c>
     </row>
     <row r="122">
@@ -97931,13 +97931,13 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0</v>
+        <v>0.4914275407791138</v>
       </c>
       <c r="JB122" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.5799999999999998</v>
       </c>
       <c r="JC122" t="n">
-        <v>1.442525561586024</v>
+        <v>0.6842577918232134</v>
       </c>
     </row>
     <row r="123">
@@ -98726,13 +98726,13 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0</v>
+        <v>0.2676181197166443</v>
       </c>
       <c r="JB123" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.4399999999999999</v>
       </c>
       <c r="JC123" t="n">
-        <v>1.442525630774216</v>
+        <v>0.684257861011406</v>
       </c>
     </row>
     <row r="124">
@@ -99521,13 +99521,13 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0</v>
+        <v>0.3999125957489014</v>
       </c>
       <c r="JB124" t="n">
-        <v>-0.7351820110112873</v>
+        <v>-0.16</v>
       </c>
       <c r="JC124" t="n">
-        <v>1.442525430128459</v>
+        <v>0.6842576603656481</v>
       </c>
     </row>
     <row r="125">
@@ -100316,13 +100316,13 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0</v>
+        <v>0.4020510315895081</v>
       </c>
       <c r="JB125" t="n">
-        <v>-0.06155603134918715</v>
+        <v>0.5100000000000001</v>
       </c>
       <c r="JC125" t="n">
-        <v>1.442525471641374</v>
+        <v>0.6842577018785635</v>
       </c>
     </row>
     <row r="126">
@@ -101111,13 +101111,13 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>1</v>
+        <v>0.5020090341567993</v>
       </c>
       <c r="JB126" t="n">
-        <v>0.2752569584818629</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="JC126" t="n">
-        <v>1.442525499316651</v>
+        <v>0.6842577295538403</v>
       </c>
     </row>
   </sheetData>

--- a/out/MLP-Mamba1_repeat_5_000006.xlsx
+++ b/out/MLP-Mamba1_repeat_5_000006.xlsx
@@ -2531,7 +2531,7 @@
         </is>
       </c>
       <c r="JA2" t="n">
-        <v>0.488022655248642</v>
+        <v>0.4880227148532867</v>
       </c>
       <c r="JB2" t="n">
         <v>-0.1600000000000001</v>
@@ -3326,7 +3326,7 @@
         </is>
       </c>
       <c r="JA3" t="n">
-        <v>0.4811038672924042</v>
+        <v>0.481103926897049</v>
       </c>
       <c r="JB3" t="n">
         <v>-0.2300000000000001</v>
@@ -11276,7 +11276,7 @@
         </is>
       </c>
       <c r="JA13" t="n">
-        <v>0.4486600756645203</v>
+        <v>0.4486601054668427</v>
       </c>
       <c r="JB13" t="n">
         <v>-0.5799999999999998</v>
@@ -12071,7 +12071,7 @@
         </is>
       </c>
       <c r="JA14" t="n">
-        <v>0.5110042095184326</v>
+        <v>0.5110042691230774</v>
       </c>
       <c r="JB14" t="n">
         <v>-0.5799999999999998</v>
@@ -12866,7 +12866,7 @@
         </is>
       </c>
       <c r="JA15" t="n">
-        <v>0.4230601787567139</v>
+        <v>0.4230602085590363</v>
       </c>
       <c r="JB15" t="n">
         <v>-0.7199999999999999</v>
@@ -13661,7 +13661,7 @@
         </is>
       </c>
       <c r="JA16" t="n">
-        <v>0.4230552613735199</v>
+        <v>0.4230553209781647</v>
       </c>
       <c r="JB16" t="n">
         <v>-0.4399999999999999</v>
@@ -16046,7 +16046,7 @@
         </is>
       </c>
       <c r="JA19" t="n">
-        <v>0.4805429577827454</v>
+        <v>0.4805430173873901</v>
       </c>
       <c r="JB19" t="n">
         <v>0.3</v>
@@ -17636,7 +17636,7 @@
         </is>
       </c>
       <c r="JA21" t="n">
-        <v>0.4384163320064545</v>
+        <v>0.4384163618087769</v>
       </c>
       <c r="JB21" t="n">
         <v>0.02000000000000007</v>
@@ -18431,7 +18431,7 @@
         </is>
       </c>
       <c r="JA22" t="n">
-        <v>0.3861115574836731</v>
+        <v>0.3861115872859955</v>
       </c>
       <c r="JB22" t="n">
         <v>-0.7199999999999999</v>
@@ -19226,7 +19226,7 @@
         </is>
       </c>
       <c r="JA23" t="n">
-        <v>0.4405272603034973</v>
+        <v>0.4405272901058197</v>
       </c>
       <c r="JB23" t="n">
         <v>-0.7199999999999999</v>
@@ -21611,7 +21611,7 @@
         </is>
       </c>
       <c r="JA26" t="n">
-        <v>0.3995951414108276</v>
+        <v>0.39959517121315</v>
       </c>
       <c r="JB26" t="n">
         <v>0.3</v>
@@ -23201,7 +23201,7 @@
         </is>
       </c>
       <c r="JA28" t="n">
-        <v>0.4622178077697754</v>
+        <v>0.4622179269790649</v>
       </c>
       <c r="JB28" t="n">
         <v>0.02000000000000007</v>
@@ -26381,7 +26381,7 @@
         </is>
       </c>
       <c r="JA32" t="n">
-        <v>0.3958992660045624</v>
+        <v>0.3958993256092072</v>
       </c>
       <c r="JB32" t="n">
         <v>-0.7199999999999999</v>
@@ -27176,7 +27176,7 @@
         </is>
       </c>
       <c r="JA33" t="n">
-        <v>0.3876829147338867</v>
+        <v>0.3876829743385315</v>
       </c>
       <c r="JB33" t="n">
         <v>-0.4399999999999999</v>
@@ -27971,7 +27971,7 @@
         </is>
       </c>
       <c r="JA34" t="n">
-        <v>0.4406318366527557</v>
+        <v>0.4406319260597229</v>
       </c>
       <c r="JB34" t="n">
         <v>-0.7199999999999999</v>
@@ -28766,7 +28766,7 @@
         </is>
       </c>
       <c r="JA35" t="n">
-        <v>0.505829393863678</v>
+        <v>0.5058293342590332</v>
       </c>
       <c r="JB35" t="n">
         <v>-0.7199999999999999</v>
@@ -32741,7 +32741,7 @@
         </is>
       </c>
       <c r="JA40" t="n">
-        <v>0.4112935364246368</v>
+        <v>0.4112935662269592</v>
       </c>
       <c r="JB40" t="n">
         <v>-0.4399999999999999</v>
@@ -34331,7 +34331,7 @@
         </is>
       </c>
       <c r="JA42" t="n">
-        <v>0.5498231649398804</v>
+        <v>0.5498231053352356</v>
       </c>
       <c r="JB42" t="n">
         <v>0.4399999999999999</v>
@@ -35921,7 +35921,7 @@
         </is>
       </c>
       <c r="JA44" t="n">
-        <v>0.5997248291969299</v>
+        <v>0.5997249484062195</v>
       </c>
       <c r="JB44" t="n">
         <v>0.4399999999999999</v>
@@ -36716,7 +36716,7 @@
         </is>
       </c>
       <c r="JA45" t="n">
-        <v>0.3964666426181793</v>
+        <v>0.3964667320251465</v>
       </c>
       <c r="JB45" t="n">
         <v>0.4399999999999999</v>
@@ -37511,7 +37511,7 @@
         </is>
       </c>
       <c r="JA46" t="n">
-        <v>0.2556702494621277</v>
+        <v>0.2556703090667725</v>
       </c>
       <c r="JB46" t="n">
         <v>0.3</v>
@@ -39101,7 +39101,7 @@
         </is>
       </c>
       <c r="JA48" t="n">
-        <v>0.6000362038612366</v>
+        <v>0.6000362634658813</v>
       </c>
       <c r="JB48" t="n">
         <v>-0.3</v>
@@ -40691,7 +40691,7 @@
         </is>
       </c>
       <c r="JA50" t="n">
-        <v>0.6309744119644165</v>
+        <v>0.6309744715690613</v>
       </c>
       <c r="JB50" t="n">
         <v>0.3</v>
@@ -43076,7 +43076,7 @@
         </is>
       </c>
       <c r="JA53" t="n">
-        <v>0.6636998653411865</v>
+        <v>0.6636998057365417</v>
       </c>
       <c r="JB53" t="n">
         <v>0.7199999999999999</v>
@@ -44666,7 +44666,7 @@
         </is>
       </c>
       <c r="JA55" t="n">
-        <v>0.7229295372962952</v>
+        <v>0.7229293584823608</v>
       </c>
       <c r="JB55" t="n">
         <v>0.7199999999999999</v>
@@ -45461,7 +45461,7 @@
         </is>
       </c>
       <c r="JA56" t="n">
-        <v>0.435119092464447</v>
+        <v>0.4351190626621246</v>
       </c>
       <c r="JB56" t="n">
         <v>0.5799999999999998</v>
@@ -46256,7 +46256,7 @@
         </is>
       </c>
       <c r="JA57" t="n">
-        <v>0.6981275677680969</v>
+        <v>0.6981274485588074</v>
       </c>
       <c r="JB57" t="n">
         <v>0.5799999999999998</v>
@@ -47051,7 +47051,7 @@
         </is>
       </c>
       <c r="JA58" t="n">
-        <v>0.6515438556671143</v>
+        <v>0.6515435576438904</v>
       </c>
       <c r="JB58" t="n">
         <v>0.5799999999999998</v>
@@ -48641,7 +48641,7 @@
         </is>
       </c>
       <c r="JA60" t="n">
-        <v>0.8129528164863586</v>
+        <v>0.8129527568817139</v>
       </c>
       <c r="JB60" t="n">
         <v>-0.02000000000000007</v>
@@ -49436,7 +49436,7 @@
         </is>
       </c>
       <c r="JA61" t="n">
-        <v>0.224351242184639</v>
+        <v>0.2243510484695435</v>
       </c>
       <c r="JB61" t="n">
         <v>-0.1600000000000001</v>
@@ -50231,7 +50231,7 @@
         </is>
       </c>
       <c r="JA62" t="n">
-        <v>0.7652610540390015</v>
+        <v>0.7652608156204224</v>
       </c>
       <c r="JB62" t="n">
         <v>-0.4399999999999999</v>
@@ -51026,7 +51026,7 @@
         </is>
       </c>
       <c r="JA63" t="n">
-        <v>0.1902934163808823</v>
+        <v>0.1902932971715927</v>
       </c>
       <c r="JB63" t="n">
         <v>-0.5799999999999998</v>
@@ -51821,7 +51821,7 @@
         </is>
       </c>
       <c r="JA64" t="n">
-        <v>0.4603838324546814</v>
+        <v>0.4603836834430695</v>
       </c>
       <c r="JB64" t="n">
         <v>-0.5799999999999998</v>
@@ -52616,7 +52616,7 @@
         </is>
       </c>
       <c r="JA65" t="n">
-        <v>0.5649556517601013</v>
+        <v>0.5649554133415222</v>
       </c>
       <c r="JB65" t="n">
         <v>-0.5799999999999998</v>
@@ -53411,7 +53411,7 @@
         </is>
       </c>
       <c r="JA66" t="n">
-        <v>0.4356594085693359</v>
+        <v>0.4356591403484344</v>
       </c>
       <c r="JB66" t="n">
         <v>-0.5799999999999998</v>
@@ -54206,7 +54206,7 @@
         </is>
       </c>
       <c r="JA67" t="n">
-        <v>0.8058984875679016</v>
+        <v>0.8058983683586121</v>
       </c>
       <c r="JB67" t="n">
         <v>-0.3</v>
@@ -55001,7 +55001,7 @@
         </is>
       </c>
       <c r="JA68" t="n">
-        <v>0.3907082676887512</v>
+        <v>0.3907081186771393</v>
       </c>
       <c r="JB68" t="n">
         <v>-0.1600000000000001</v>
@@ -55796,7 +55796,7 @@
         </is>
       </c>
       <c r="JA69" t="n">
-        <v>0.7346447110176086</v>
+        <v>0.7346444725990295</v>
       </c>
       <c r="JB69" t="n">
         <v>0.4399999999999999</v>
@@ -56591,7 +56591,7 @@
         </is>
       </c>
       <c r="JA70" t="n">
-        <v>0.7675833106040955</v>
+        <v>0.7675831913948059</v>
       </c>
       <c r="JB70" t="n">
         <v>0.1600000000000001</v>
@@ -57386,7 +57386,7 @@
         </is>
       </c>
       <c r="JA71" t="n">
-        <v>0.3728429973125458</v>
+        <v>0.3728427290916443</v>
       </c>
       <c r="JB71" t="n">
         <v>0.16</v>
@@ -58181,7 +58181,7 @@
         </is>
       </c>
       <c r="JA72" t="n">
-        <v>0.16764797270298</v>
+        <v>0.1676478385925293</v>
       </c>
       <c r="JB72" t="n">
         <v>-0.7199999999999999</v>
@@ -58976,7 +58976,7 @@
         </is>
       </c>
       <c r="JA73" t="n">
-        <v>0.5131186246871948</v>
+        <v>0.5131183862686157</v>
       </c>
       <c r="JB73" t="n">
         <v>-0.9999999999999998</v>
@@ -59771,7 +59771,7 @@
         </is>
       </c>
       <c r="JA74" t="n">
-        <v>0.2291493117809296</v>
+        <v>0.2291491329669952</v>
       </c>
       <c r="JB74" t="n">
         <v>-0.9999999999999998</v>
@@ -60566,7 +60566,7 @@
         </is>
       </c>
       <c r="JA75" t="n">
-        <v>0.4852877855300903</v>
+        <v>0.4852877259254456</v>
       </c>
       <c r="JB75" t="n">
         <v>-0.8599999999999999</v>
@@ -61361,7 +61361,7 @@
         </is>
       </c>
       <c r="JA76" t="n">
-        <v>0.4039653837680817</v>
+        <v>0.4039651453495026</v>
       </c>
       <c r="JB76" t="n">
         <v>-0.7199999999999999</v>
@@ -62156,7 +62156,7 @@
         </is>
       </c>
       <c r="JA77" t="n">
-        <v>0.5301371216773987</v>
+        <v>0.5301369428634644</v>
       </c>
       <c r="JB77" t="n">
         <v>-0.7199999999999999</v>
@@ -62951,7 +62951,7 @@
         </is>
       </c>
       <c r="JA78" t="n">
-        <v>0.5338163375854492</v>
+        <v>0.5338160991668701</v>
       </c>
       <c r="JB78" t="n">
         <v>0.16</v>
@@ -63746,7 +63746,7 @@
         </is>
       </c>
       <c r="JA79" t="n">
-        <v>0.393704354763031</v>
+        <v>0.3937041163444519</v>
       </c>
       <c r="JB79" t="n">
         <v>0.16</v>
@@ -64541,7 +64541,7 @@
         </is>
       </c>
       <c r="JA80" t="n">
-        <v>0.6042994260787964</v>
+        <v>0.6042992472648621</v>
       </c>
       <c r="JB80" t="n">
         <v>0.3</v>
@@ -65336,7 +65336,7 @@
         </is>
       </c>
       <c r="JA81" t="n">
-        <v>0.4034383893013</v>
+        <v>0.4034381210803986</v>
       </c>
       <c r="JB81" t="n">
         <v>0.4399999999999999</v>
@@ -66131,7 +66131,7 @@
         </is>
       </c>
       <c r="JA82" t="n">
-        <v>0.7514288425445557</v>
+        <v>0.7514286637306213</v>
       </c>
       <c r="JB82" t="n">
         <v>0.7199999999999999</v>
@@ -66926,7 +66926,7 @@
         </is>
       </c>
       <c r="JA83" t="n">
-        <v>0.5877249240875244</v>
+        <v>0.5877246856689453</v>
       </c>
       <c r="JB83" t="n">
         <v>0.4399999999999999</v>
@@ -67721,7 +67721,7 @@
         </is>
       </c>
       <c r="JA84" t="n">
-        <v>0.7363027334213257</v>
+        <v>0.7363025546073914</v>
       </c>
       <c r="JB84" t="n">
         <v>0.4399999999999999</v>
@@ -68516,7 +68516,7 @@
         </is>
       </c>
       <c r="JA85" t="n">
-        <v>0.4857492744922638</v>
+        <v>0.4857489168643951</v>
       </c>
       <c r="JB85" t="n">
         <v>0.16</v>
@@ -69311,7 +69311,7 @@
         </is>
       </c>
       <c r="JA86" t="n">
-        <v>0.4740878045558929</v>
+        <v>0.4740874767303467</v>
       </c>
       <c r="JB86" t="n">
         <v>-0.4399999999999999</v>
@@ -70106,7 +70106,7 @@
         </is>
       </c>
       <c r="JA87" t="n">
-        <v>0.5162799954414368</v>
+        <v>0.5162795782089233</v>
       </c>
       <c r="JB87" t="n">
         <v>-0.7199999999999999</v>
@@ -70901,7 +70901,7 @@
         </is>
       </c>
       <c r="JA88" t="n">
-        <v>0.7422133684158325</v>
+        <v>0.7422130703926086</v>
       </c>
       <c r="JB88" t="n">
         <v>-0.5799999999999998</v>
@@ -71696,7 +71696,7 @@
         </is>
       </c>
       <c r="JA89" t="n">
-        <v>0.3018356263637543</v>
+        <v>0.3018353581428528</v>
       </c>
       <c r="JB89" t="n">
         <v>-0.3</v>
@@ -72491,7 +72491,7 @@
         </is>
       </c>
       <c r="JA90" t="n">
-        <v>0.4955836832523346</v>
+        <v>0.4955832660198212</v>
       </c>
       <c r="JB90" t="n">
         <v>-0.02000000000000007</v>
@@ -73286,7 +73286,7 @@
         </is>
       </c>
       <c r="JA91" t="n">
-        <v>0.5621458888053894</v>
+        <v>0.5621455311775208</v>
       </c>
       <c r="JB91" t="n">
         <v>0.3</v>
@@ -74081,7 +74081,7 @@
         </is>
       </c>
       <c r="JA92" t="n">
-        <v>0.5481483936309814</v>
+        <v>0.548147976398468</v>
       </c>
       <c r="JB92" t="n">
         <v>0.3</v>
@@ -74876,7 +74876,7 @@
         </is>
       </c>
       <c r="JA93" t="n">
-        <v>0.3974269330501556</v>
+        <v>0.397426575422287</v>
       </c>
       <c r="JB93" t="n">
         <v>0.16</v>
@@ -75671,7 +75671,7 @@
         </is>
       </c>
       <c r="JA94" t="n">
-        <v>0.3201610147953033</v>
+        <v>0.3201607167720795</v>
       </c>
       <c r="JB94" t="n">
         <v>0.16</v>
@@ -76466,7 +76466,7 @@
         </is>
       </c>
       <c r="JA95" t="n">
-        <v>0.3741748034954071</v>
+        <v>0.3741744458675385</v>
       </c>
       <c r="JB95" t="n">
         <v>-0.4399999999999999</v>
@@ -77261,7 +77261,7 @@
         </is>
       </c>
       <c r="JA96" t="n">
-        <v>0.6763342022895813</v>
+        <v>0.6763339638710022</v>
       </c>
       <c r="JB96" t="n">
         <v>-0.4399999999999999</v>
@@ -78056,7 +78056,7 @@
         </is>
       </c>
       <c r="JA97" t="n">
-        <v>0.6145511269569397</v>
+        <v>0.6145508289337158</v>
       </c>
       <c r="JB97" t="n">
         <v>-0.4399999999999999</v>
@@ -78851,7 +78851,7 @@
         </is>
       </c>
       <c r="JA98" t="n">
-        <v>0.4709202945232391</v>
+        <v>0.4709198772907257</v>
       </c>
       <c r="JB98" t="n">
         <v>-0.4399999999999999</v>
@@ -79646,7 +79646,7 @@
         </is>
       </c>
       <c r="JA99" t="n">
-        <v>0.2231430560350418</v>
+        <v>0.2231428623199463</v>
       </c>
       <c r="JB99" t="n">
         <v>-0.7199999999999999</v>
@@ -80441,7 +80441,7 @@
         </is>
       </c>
       <c r="JA100" t="n">
-        <v>0.4341157674789429</v>
+        <v>0.4341153502464294</v>
       </c>
       <c r="JB100" t="n">
         <v>-0.9999999999999998</v>
@@ -81236,7 +81236,7 @@
         </is>
       </c>
       <c r="JA101" t="n">
-        <v>0.2131999582052231</v>
+        <v>0.213199719786644</v>
       </c>
       <c r="JB101" t="n">
         <v>-0.7199999999999999</v>
@@ -82031,7 +82031,7 @@
         </is>
       </c>
       <c r="JA102" t="n">
-        <v>0.4170821309089661</v>
+        <v>0.4170818626880646</v>
       </c>
       <c r="JB102" t="n">
         <v>-0.7199999999999999</v>
@@ -82826,7 +82826,7 @@
         </is>
       </c>
       <c r="JA103" t="n">
-        <v>0.6004751920700073</v>
+        <v>0.6004748940467834</v>
       </c>
       <c r="JB103" t="n">
         <v>-0.7199999999999999</v>
@@ -83621,7 +83621,7 @@
         </is>
       </c>
       <c r="JA104" t="n">
-        <v>0.2639464437961578</v>
+        <v>0.2639462947845459</v>
       </c>
       <c r="JB104" t="n">
         <v>-0.7199999999999999</v>
@@ -84416,7 +84416,7 @@
         </is>
       </c>
       <c r="JA105" t="n">
-        <v>0.3377128541469574</v>
+        <v>0.3377125859260559</v>
       </c>
       <c r="JB105" t="n">
         <v>-0.7199999999999999</v>
@@ -85211,7 +85211,7 @@
         </is>
       </c>
       <c r="JA106" t="n">
-        <v>0.4114673435688019</v>
+        <v>0.4114671051502228</v>
       </c>
       <c r="JB106" t="n">
         <v>-0.9999999999999998</v>
@@ -86006,7 +86006,7 @@
         </is>
       </c>
       <c r="JA107" t="n">
-        <v>0.2656219303607941</v>
+        <v>0.2656218111515045</v>
       </c>
       <c r="JB107" t="n">
         <v>-0.9999999999999998</v>
@@ -86801,7 +86801,7 @@
         </is>
       </c>
       <c r="JA108" t="n">
-        <v>0.2876636385917664</v>
+        <v>0.2876635193824768</v>
       </c>
       <c r="JB108" t="n">
         <v>-0.7199999999999999</v>
@@ -87596,7 +87596,7 @@
         </is>
       </c>
       <c r="JA109" t="n">
-        <v>0.4344042241573334</v>
+        <v>0.434404045343399</v>
       </c>
       <c r="JB109" t="n">
         <v>-0.7199999999999999</v>
@@ -88391,7 +88391,7 @@
         </is>
       </c>
       <c r="JA110" t="n">
-        <v>0.4746588468551636</v>
+        <v>0.4746586382389069</v>
       </c>
       <c r="JB110" t="n">
         <v>-0.1199999999999999</v>
@@ -89186,7 +89186,7 @@
         </is>
       </c>
       <c r="JA111" t="n">
-        <v>0.3380211591720581</v>
+        <v>0.3380209505558014</v>
       </c>
       <c r="JB111" t="n">
         <v>-0.1199999999999999</v>
@@ -89981,7 +89981,7 @@
         </is>
       </c>
       <c r="JA112" t="n">
-        <v>0.2806555330753326</v>
+        <v>0.2806553840637207</v>
       </c>
       <c r="JB112" t="n">
         <v>0.16</v>
@@ -90776,7 +90776,7 @@
         </is>
       </c>
       <c r="JA113" t="n">
-        <v>0.3019035160541534</v>
+        <v>0.3019033670425415</v>
       </c>
       <c r="JB113" t="n">
         <v>-0.1199999999999999</v>
@@ -91571,7 +91571,7 @@
         </is>
       </c>
       <c r="JA114" t="n">
-        <v>0.487054854631424</v>
+        <v>0.4870550632476807</v>
       </c>
       <c r="JB114" t="n">
         <v>0.1600000000000001</v>
@@ -92366,7 +92366,7 @@
         </is>
       </c>
       <c r="JA115" t="n">
-        <v>0.3261367082595825</v>
+        <v>0.3261364996433258</v>
       </c>
       <c r="JB115" t="n">
         <v>0.16</v>
@@ -93161,7 +93161,7 @@
         </is>
       </c>
       <c r="JA116" t="n">
-        <v>0.4251779615879059</v>
+        <v>0.4251777529716492</v>
       </c>
       <c r="JB116" t="n">
         <v>0.4399999999999999</v>
@@ -93956,7 +93956,7 @@
         </is>
       </c>
       <c r="JA117" t="n">
-        <v>0.3146539032459259</v>
+        <v>0.314653754234314</v>
       </c>
       <c r="JB117" t="n">
         <v>0.4399999999999999</v>
@@ -94751,7 +94751,7 @@
         </is>
       </c>
       <c r="JA118" t="n">
-        <v>0.7171016931533813</v>
+        <v>0.7171015739440918</v>
       </c>
       <c r="JB118" t="n">
         <v>0.4399999999999999</v>
@@ -95546,7 +95546,7 @@
         </is>
       </c>
       <c r="JA119" t="n">
-        <v>0.6038730144500732</v>
+        <v>0.6038728952407837</v>
       </c>
       <c r="JB119" t="n">
         <v>0.1600000000000001</v>
@@ -96341,7 +96341,7 @@
         </is>
       </c>
       <c r="JA120" t="n">
-        <v>0.2751888334751129</v>
+        <v>0.2751887142658234</v>
       </c>
       <c r="JB120" t="n">
         <v>0.4399999999999999</v>
@@ -97136,7 +97136,7 @@
         </is>
       </c>
       <c r="JA121" t="n">
-        <v>0.351144939661026</v>
+        <v>0.3511447608470917</v>
       </c>
       <c r="JB121" t="n">
         <v>0.16</v>
@@ -97931,7 +97931,7 @@
         </is>
       </c>
       <c r="JA122" t="n">
-        <v>0.4914275407791138</v>
+        <v>0.4914273619651794</v>
       </c>
       <c r="JB122" t="n">
         <v>-0.5799999999999998</v>
@@ -98726,7 +98726,7 @@
         </is>
       </c>
       <c r="JA123" t="n">
-        <v>0.2676181197166443</v>
+        <v>0.2676179707050323</v>
       </c>
       <c r="JB123" t="n">
         <v>-0.4399999999999999</v>
@@ -99521,7 +99521,7 @@
         </is>
       </c>
       <c r="JA124" t="n">
-        <v>0.3999125957489014</v>
+        <v>0.3999124467372894</v>
       </c>
       <c r="JB124" t="n">
         <v>-0.16</v>
@@ -100316,7 +100316,7 @@
         </is>
       </c>
       <c r="JA125" t="n">
-        <v>0.4020510315895081</v>
+        <v>0.4020508527755737</v>
       </c>
       <c r="JB125" t="n">
         <v>0.5100000000000001</v>
@@ -101111,7 +101111,7 @@
         </is>
       </c>
       <c r="JA126" t="n">
-        <v>0.5020090341567993</v>
+        <v>0.502008855342865</v>
       </c>
       <c r="JB126" t="n">
         <v>0.5800000000000001</v>
